--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -23561,13 +23561,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B840A412-856F-4666-B7A9-2FBADD5A0A0F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D13B788E-43D5-4583-B9A9-DD7EF172E3A9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02750FD1-8FF8-40F4-9A4D-67066AD9518F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D036120A-038E-4F55-863A-39A210D7E364}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1D8F1AB-7847-4B68-8139-912B839900C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAC2DB19-8E25-4E99-B82B-98C2DBF89EFE}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -23561,13 +23561,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D13B788E-43D5-4583-B9A9-DD7EF172E3A9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33B9D50A-56F9-4D82-AF82-05683CB261F1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D036120A-038E-4F55-863A-39A210D7E364}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFB94600-236C-437D-B2D0-B5427426F268}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAC2DB19-8E25-4E99-B82B-98C2DBF89EFE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CF91148-9A33-4408-9099-658FA820F338}"/>
 </file>